--- a/ToxCast_model/experiments/prediction/DART_MTL/DART_Multi+DL_AddData_251204.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL/DART_Multi+DL_AddData_251204.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hwangjin-won/Desktop/Univ./Intern/Projects/DART_Multi+DL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C8CB5B-2AE5-F84A-B23D-EF36E45186F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A181EB5A-F014-BD4F-9954-0A240CF8720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="2160" windowWidth="26700" windowHeight="15200" xr2:uid="{0ACCCFCA-B604-4A4F-B60D-7EF4A1A3E350}"/>
+    <workbookView xWindow="33360" yWindow="2160" windowWidth="26700" windowHeight="15200" activeTab="1" xr2:uid="{0ACCCFCA-B604-4A4F-B60D-7EF4A1A3E350}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="assay_list" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="245">
   <si>
     <t>DTXSID0021836</t>
   </si>
@@ -759,6 +759,21 @@
   <si>
     <t>SMILES</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>RDKit</t>
+  </si>
+  <si>
+    <t>Layered</t>
+  </si>
+  <si>
+    <t>MACCS</t>
+  </si>
+  <si>
+    <t>Morgan</t>
   </si>
 </sst>
 </file>
@@ -2084,310 +2099,496 @@
       <c r="A2" t="s">
         <v>99</v>
       </c>
+      <c r="C2" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
+      <c r="C3" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>101</v>
       </c>
+      <c r="C4" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>102</v>
       </c>
+      <c r="C5" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>103</v>
       </c>
+      <c r="C6" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>104</v>
       </c>
+      <c r="C7" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>105</v>
       </c>
+      <c r="C8" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>106</v>
       </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>107</v>
       </c>
+      <c r="C10" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>108</v>
       </c>
+      <c r="C11" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>109</v>
       </c>
+      <c r="C12" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>110</v>
       </c>
+      <c r="C13" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>111</v>
       </c>
+      <c r="C14" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>112</v>
       </c>
+      <c r="C15" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="C16" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="C17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="C18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="C19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="C20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="C21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="C22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="C23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="C24" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="C25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="C26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="C27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="C28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="C29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="C30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="C31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="C32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="C33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="C34" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="C35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="C36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="C37" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="C39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="C40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="C41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="C42" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="C43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="C44" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="C45" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="C46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="C47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="C48" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="C49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="C50" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="C51" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="C52" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="C53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="C54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="C55" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="C56" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="C57" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="C58" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="C59" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="C60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="C61" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="C62" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>160</v>
+      </c>
+      <c r="C63" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
